--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno_base.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno_base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4358671-703B-453C-9431-DBB2BDAB6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52E3416-B315-45A0-896F-37C2125BF41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7545" yWindow="2115" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -83,6 +83,18 @@
   </si>
   <si>
     <t>Lucky</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellCooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellAutoRechargeTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxSpellCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -406,7 +418,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24.625" customWidth="1"/>
@@ -557,6 +569,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
